--- a/bts-gpme/tp-1083/ressources/R05_Cyber_RGPD.xlsx
+++ b/bts-gpme/tp-1083/ressources/R05_Cyber_RGPD.xlsx
@@ -2,9 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applications" sheetId="1" r:id="Rcec14067d95d454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronologie_incident" sheetId="2" r:id="R0947f5c2d5ec4bb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traitements_donnees" sheetId="3" r:id="R4c2fac83695547ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Applications" sheetId="1" r:id="R90e3dd004c6b45e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chronologie_incident" sheetId="2" r:id="R63fc65de29d743c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traitements_donnees" sheetId="3" r:id="R8cbb78d917ea4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sauvegardes" sheetId="4" r:id="Rb20ae6fe084e4b72"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -32,8 +33,24 @@
       <x:color rgb="FF173F45"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -50,6 +67,56 @@
         <x:fgColor rgb="FFDDEFF2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -58,7 +125,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="68">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -92,6 +159,130 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -341,52 +532,65 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="35" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="40" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="58" t="str">
         <x:v>DONNÉES PÉDAGOGIQUES SIMULÉES — architecture, comptes et incidents ne décrivent pas le système réel de 1083.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="B1" s="59"/>
+      <x:c r="C1" s="59"/>
+      <x:c r="D1" s="59"/>
+      <x:c r="E1" s="59"/>
+      <x:c r="F1" s="59"/>
+      <x:c r="G1" s="59"/>
+    </x:row>
+    <x:row r="2" ht="38" customHeight="1">
+      <x:c r="A2" s="38" t="str">
+        <x:v>La criticité métier indique l’importance du service pour l’activité ; elle ne mesure pas, à elle seule, le niveau de risque cyber.</x:v>
+      </x:c>
+      <x:c r="B2" s="38"/>
+      <x:c r="C2" s="38"/>
+      <x:c r="D2" s="38"/>
+      <x:c r="E2" s="38"/>
+      <x:c r="F2" s="38"/>
+      <x:c r="G2" s="38"/>
+    </x:row>
+    <x:row r="3" ht="40" customHeight="1">
+      <x:c r="A3" s="41" t="str">
         <x:v>Application / ressource</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B3" s="41" t="str">
         <x:v>Usage</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="C3" s="41" t="str">
         <x:v>Données traitées</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str">
+      <x:c r="D3" s="41" t="str">
         <x:v>Criticité métier</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str">
+      <x:c r="E3" s="41" t="str">
         <x:v>Authentification</x:v>
       </x:c>
-      <x:c r="F3" s="14" t="str">
+      <x:c r="F3" s="41" t="str">
         <x:v>MFA</x:v>
       </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>Sauvegarde annoncée</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="str">
-        <x:v>Dernier test de restauration</x:v>
-      </x:c>
-      <x:c r="I3" s="14" t="str">
+      <x:c r="G3" s="41" t="str">
         <x:v>Accès / observation</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4">
+      <x:c r="H3" s="14"/>
+      <x:c r="I3" s="14"/>
+    </x:row>
+    <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="16" t="str">
         <x:v>Site e-commerce (Magento 2)</x:v>
       </x:c>
@@ -406,16 +610,12 @@
         <x:v>Partielle</x:v>
       </x:c>
       <x:c r="G4" s="16" t="str">
-        <x:v>Quotidienne</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="str">
-        <x:v>14/02/2026</x:v>
-      </x:c>
-      <x:c r="I4" s="16" t="str">
         <x:v>Le compte admin partagé est connu de 3 personnes.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="H4" s="16"/>
+      <x:c r="I4" s="16"/>
+    </x:row>
+    <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="16" t="str">
         <x:v>Messagerie cloud</x:v>
       </x:c>
@@ -435,16 +635,12 @@
         <x:v>Oui pour direction ; non pour 4 comptes</x:v>
       </x:c>
       <x:c r="G5" s="16" t="str">
-        <x:v>Fournisseur cloud</x:v>
-      </x:c>
-      <x:c r="H5" s="16" t="str">
-        <x:v>Non documenté</x:v>
-      </x:c>
-      <x:c r="I5" s="16" t="str">
         <x:v>Redirections vers messagerie personnelle interdites mais contrôle non tracé.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6">
+      <x:c r="H5" s="16"/>
+      <x:c r="I5" s="16"/>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="16" t="str">
         <x:v>CRM revendeurs</x:v>
       </x:c>
@@ -464,16 +660,12 @@
         <x:v>Non</x:v>
       </x:c>
       <x:c r="G6" s="16" t="str">
-        <x:v>Hebdomadaire</x:v>
-      </x:c>
-      <x:c r="H6" s="16" t="str">
-        <x:v>03/11/2025</x:v>
-      </x:c>
-      <x:c r="I6" s="16" t="str">
-        <x:v>Export CSV mensuel conservé sur un dossier partagé.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>Accès à revoir après mobilité interne ; une tentative d’accès est signalée dans la chronologie.</x:v>
+      </x:c>
+      <x:c r="H6" s="16"/>
+      <x:c r="I6" s="16"/>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="16" t="str">
         <x:v>Dossier partagé RH</x:v>
       </x:c>
@@ -493,16 +685,12 @@
         <x:v>Non</x:v>
       </x:c>
       <x:c r="G7" s="16" t="str">
-        <x:v>Quotidienne</x:v>
-      </x:c>
-      <x:c r="H7" s="16" t="str">
-        <x:v>18/06/2026</x:v>
-      </x:c>
-      <x:c r="I7" s="16" t="str">
-        <x:v>Droits hérités d'un ancien groupe 'Tous-bureaux'.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>Droits hérités d'un ancien groupe « Tous-bureaux ».</x:v>
+      </x:c>
+      <x:c r="H7" s="16"/>
+      <x:c r="I7" s="16"/>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="16" t="str">
         <x:v>Logiciel comptable</x:v>
       </x:c>
@@ -522,16 +710,12 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="G8" s="16" t="str">
-        <x:v>Quotidienne</x:v>
-      </x:c>
-      <x:c r="H8" s="16" t="str">
-        <x:v>02/09/2026</x:v>
-      </x:c>
-      <x:c r="I8" s="16" t="str">
         <x:v>Accès externe via prestataire comptable.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9">
+      <x:c r="H8" s="16"/>
+      <x:c r="I8" s="16"/>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="16" t="str">
         <x:v>Postes atelier</x:v>
       </x:c>
@@ -551,16 +735,12 @@
         <x:v>Non</x:v>
       </x:c>
       <x:c r="G9" s="16" t="str">
-        <x:v>Hebdomadaire</x:v>
-      </x:c>
-      <x:c r="H9" s="16" t="str">
-        <x:v>Jamais</x:v>
-      </x:c>
-      <x:c r="I9" s="16" t="str">
         <x:v>Deux postes ne sont pas chiffrés.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10">
+      <x:c r="H9" s="16"/>
+      <x:c r="I9" s="16"/>
+    </x:row>
+    <x:row r="10" ht="48" customHeight="1">
       <x:c r="A10" s="16" t="str">
         <x:v>Outil newsletter</x:v>
       </x:c>
@@ -580,16 +760,12 @@
         <x:v>Oui</x:v>
       </x:c>
       <x:c r="G10" s="16" t="str">
-        <x:v>Fournisseur cloud</x:v>
-      </x:c>
-      <x:c r="H10" s="16" t="str">
-        <x:v>Non applicable</x:v>
-      </x:c>
-      <x:c r="I10" s="16" t="str">
-        <x:v>Suppression des désabonnés automatisée.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>Compte d’équipe ; suppression des désabonnés automatisée.</x:v>
+      </x:c>
+      <x:c r="H10" s="16"/>
+      <x:c r="I10" s="16"/>
+    </x:row>
+    <x:row r="11" ht="48" customHeight="1">
       <x:c r="A11" s="16" t="str">
         <x:v>NAS local</x:v>
       </x:c>
@@ -609,22 +785,19 @@
         <x:v>Non</x:v>
       </x:c>
       <x:c r="G11" s="16" t="str">
-        <x:v>Synchronisation quotidienne</x:v>
-      </x:c>
-      <x:c r="H11" s="16" t="str">
-        <x:v>27/01/2026</x:v>
-      </x:c>
-      <x:c r="I11" s="16" t="str">
-        <x:v>La sauvegarde reste connectée au réseau en permanence.</x:v>
-      </x:c>
+        <x:v>Accessible depuis le réseau interne ; les éléments relatifs aux sauvegardes sont regroupés dans l’onglet « Sauvegardes ».</x:v>
+      </x:c>
+      <x:c r="H11" s="16"/>
+      <x:c r="I11" s="16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A1:G1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f0f24a40af4146"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d021b5c4dd94f2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -634,52 +807,59 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="55" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="62" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="62" t="str">
         <x:v>SCÉNARIO FICTIF — incident construit uniquement pour l'apprentissage de la gestion d'un risque cyber et d'une violation de données.</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="B1" s="63"/>
+      <x:c r="C1" s="63"/>
+      <x:c r="D1" s="63"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="38" t="str">
+        <x:v>Les formulations sont volontairement brutes : à vous de qualifier ce qui est confirmé, ce qui constitue un indice, une hypothèse ou une information encore à vérifier.</x:v>
+      </x:c>
+      <x:c r="B2" s="38"/>
+      <x:c r="C2" s="38"/>
+      <x:c r="D2" s="38"/>
+    </x:row>
+    <x:row r="3" ht="35" customHeight="1">
+      <x:c r="A3" s="41" t="str">
         <x:v>Heure</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
-        <x:v>Fait observé</x:v>
-      </x:c>
-      <x:c r="C3" s="14" t="str">
-        <x:v>Source</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="str">
-        <x:v>Information certaine ?</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="str">
+      <x:c r="B3" s="41" t="str">
+        <x:v>Élément relevé</x:v>
+      </x:c>
+      <x:c r="C3" s="41" t="str">
+        <x:v>Source / origine</x:v>
+      </x:c>
+      <x:c r="D3" s="41" t="str">
         <x:v>Action déjà réalisée</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4">
+      <x:c r="E3" s="14"/>
+    </x:row>
+    <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="16" t="str">
         <x:v>08:41</x:v>
       </x:c>
       <x:c r="B4" s="16" t="str">
-        <x:v>Réception d'un courriel demandant de 'revalider' l'accès à un outil de livraison.</x:v>
+        <x:v>Réception d'un courriel demandant de « revalider » l'accès à un outil de livraison.</x:v>
       </x:c>
       <x:c r="C4" s="16" t="str">
         <x:v>Boîte service clients</x:v>
       </x:c>
       <x:c r="D4" s="16" t="str">
-        <x:v>Oui</x:v>
-      </x:c>
-      <x:c r="E4" s="16" t="str">
         <x:v>Aucune</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="E4" s="16"/>
+    </x:row>
+    <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="16" t="str">
         <x:v>08:47</x:v>
       </x:c>
@@ -690,13 +870,11 @@
         <x:v>Déclaration collaboratrice</x:v>
       </x:c>
       <x:c r="D5" s="16" t="str">
-        <x:v>Oui</x:v>
-      </x:c>
-      <x:c r="E5" s="16" t="str">
         <x:v>Aucune</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6">
+      <x:c r="E5" s="16"/>
+    </x:row>
+    <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="16" t="str">
         <x:v>08:53</x:v>
       </x:c>
@@ -707,13 +885,11 @@
         <x:v>Journal de connexion</x:v>
       </x:c>
       <x:c r="D6" s="16" t="str">
-        <x:v>Oui</x:v>
-      </x:c>
-      <x:c r="E6" s="16" t="str">
         <x:v>Mot de passe modifié à 09:22</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7">
+      <x:c r="E6" s="16"/>
+    </x:row>
+    <x:row r="7" ht="48" customHeight="1">
       <x:c r="A7" s="16" t="str">
         <x:v>09:01</x:v>
       </x:c>
@@ -724,30 +900,26 @@
         <x:v>Journal de messagerie</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
-        <x:v>Oui</x:v>
-      </x:c>
-      <x:c r="E7" s="16" t="str">
         <x:v>Règle supprimée à 09:24</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8">
+      <x:c r="E7" s="16"/>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="16" t="str">
         <x:v>09:12</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
-        <x:v>Téléchargement d'un fichier nommé 'clients_retours_2026.csv' depuis le dossier partagé.</x:v>
+        <x:v>Téléchargement d'un fichier nommé « clients_retours_2026.csv » depuis le dossier partagé avec le compte compromis.</x:v>
       </x:c>
       <x:c r="C8" s="16" t="str">
         <x:v>Journal NAS</x:v>
       </x:c>
       <x:c r="D8" s="16" t="str">
-        <x:v>Oui</x:v>
-      </x:c>
-      <x:c r="E8" s="16" t="str">
         <x:v>Compte désactivé à 09:26</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9">
+      <x:c r="E8" s="16"/>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="16" t="str">
         <x:v>09:35</x:v>
       </x:c>
@@ -758,13 +930,11 @@
         <x:v>Responsable e-commerce</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
-        <x:v>À confirmer</x:v>
-      </x:c>
-      <x:c r="E9" s="16" t="str">
         <x:v>Copie du fichier isolée</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10">
+      <x:c r="E9" s="16"/>
+    </x:row>
+    <x:row r="10" ht="48" customHeight="1">
       <x:c r="A10" s="16" t="str">
         <x:v>10:10</x:v>
       </x:c>
@@ -775,13 +945,11 @@
         <x:v>Première analyse</x:v>
       </x:c>
       <x:c r="D10" s="16" t="str">
-        <x:v>Oui à ce stade</x:v>
-      </x:c>
-      <x:c r="E10" s="16" t="str">
         <x:v>Investigation en cours</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11">
+      <x:c r="E10" s="16"/>
+    </x:row>
+    <x:row r="11" ht="48" customHeight="1">
       <x:c r="A11" s="16" t="str">
         <x:v>11:40</x:v>
       </x:c>
@@ -792,13 +960,11 @@
         <x:v>Extraction</x:v>
       </x:c>
       <x:c r="D11" s="16" t="str">
-        <x:v>À fiabiliser</x:v>
-      </x:c>
-      <x:c r="E11" s="16" t="str">
         <x:v>Dédoublonnage à faire</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12">
+      <x:c r="E11" s="16"/>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
       <x:c r="A12" s="16" t="str">
         <x:v>14:20</x:v>
       </x:c>
@@ -809,19 +975,18 @@
         <x:v>Prestataire</x:v>
       </x:c>
       <x:c r="D12" s="16" t="str">
-        <x:v>Oui</x:v>
-      </x:c>
-      <x:c r="E12" s="16" t="str">
         <x:v>Journaux CRM demandés</x:v>
       </x:c>
+      <x:c r="E12" s="16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:D2"/>
+    <x:mergeCell ref="A1:D1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raebc353121304e05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f4470a357de4a77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -834,44 +999,55 @@
     <x:col min="2" max="2" width="26" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="38" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="32" customHeight="1">
-      <x:c r="A1" s="6" t="str">
-        <x:v>EXTRAIT PÉDAGOGIQUE SIMULÉ DU REGISTRE — à analyser, compléter et corriger.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="14" t="str">
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="66" t="str">
+        <x:v>EXTRAIT PÉDAGOGIQUE SIMULÉ DES TRAITEMENTS — à utiliser pour identifier les données et les personnes susceptibles d’être concernées par l’incident.</x:v>
+      </x:c>
+      <x:c r="B1" s="67"/>
+      <x:c r="C1" s="67"/>
+      <x:c r="D1" s="67"/>
+      <x:c r="E1" s="67"/>
+      <x:c r="F1" s="67"/>
+    </x:row>
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="38" t="str">
+        <x:v>Ne réalisez pas ici un audit général de conformité RGPD : concentrez-vous sur le périmètre de l’incident et sur ce qui est réellement établi par les pièces.</x:v>
+      </x:c>
+      <x:c r="B2" s="38"/>
+      <x:c r="C2" s="38"/>
+      <x:c r="D2" s="38"/>
+      <x:c r="E2" s="38"/>
+      <x:c r="F2" s="38"/>
+    </x:row>
+    <x:row r="3" ht="40" customHeight="1">
+      <x:c r="A3" s="41" t="str">
         <x:v>Traitement</x:v>
       </x:c>
-      <x:c r="B3" s="14" t="str">
+      <x:c r="B3" s="41" t="str">
         <x:v>Finalité</x:v>
       </x:c>
-      <x:c r="C3" s="14" t="str">
+      <x:c r="C3" s="41" t="str">
         <x:v>Personnes concernées</x:v>
       </x:c>
-      <x:c r="D3" s="14" t="str">
+      <x:c r="D3" s="41" t="str">
         <x:v>Données principales</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str">
-        <x:v>Base / justification indiquée</x:v>
-      </x:c>
-      <x:c r="F3" s="14" t="str">
-        <x:v>Durée indiquée</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>Destinataires</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="str">
-        <x:v>Observation</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+      <x:c r="E3" s="41" t="str">
+        <x:v>Destinataires / accès connus</x:v>
+      </x:c>
+      <x:c r="F3" s="41" t="str">
+        <x:v>Observation liée au scénario</x:v>
+      </x:c>
+      <x:c r="G3" s="14"/>
+      <x:c r="H3" s="14"/>
+    </x:row>
+    <x:row r="4" ht="58" customHeight="1">
       <x:c r="A4" s="16" t="str">
         <x:v>Commandes e-commerce</x:v>
       </x:c>
@@ -885,19 +1061,15 @@
         <x:v>Identité, coordonnées, commande, paiement tokenisé</x:v>
       </x:c>
       <x:c r="E4" s="16" t="str">
-        <x:v>Contrat</x:v>
+        <x:v>Logistique, comptabilité</x:v>
       </x:c>
       <x:c r="F4" s="16" t="str">
-        <x:v>10 ans pour toutes les données</x:v>
-      </x:c>
-      <x:c r="G4" s="16" t="str">
-        <x:v>Logistique, comptabilité</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="str">
-        <x:v>La durée unique de 10 ans mérite d'être distinguée selon les données.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>Aucun élément du scénario ne confirme à lui seul un accès à l'ensemble de la base de commandes.</x:v>
+      </x:c>
+      <x:c r="G4" s="16"/>
+      <x:c r="H4" s="16"/>
+    </x:row>
+    <x:row r="5" ht="58" customHeight="1">
       <x:c r="A5" s="16" t="str">
         <x:v>Compte client</x:v>
       </x:c>
@@ -911,19 +1083,15 @@
         <x:v>Identité, adresses, historique</x:v>
       </x:c>
       <x:c r="E5" s="16" t="str">
-        <x:v>Contrat / intérêt légitime</x:v>
+        <x:v>Service clients</x:v>
       </x:c>
       <x:c r="F5" s="16" t="str">
-        <x:v>Tant que le compte existe</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="str">
-        <x:v>Service clients</x:v>
-      </x:c>
-      <x:c r="H5" s="16" t="str">
-        <x:v>Processus d'inactivité non défini.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>Aucun élément du scénario ne confirme à ce stade un accès aux comptes clients.</x:v>
+      </x:c>
+      <x:c r="G5" s="16"/>
+      <x:c r="H5" s="16"/>
+    </x:row>
+    <x:row r="6" ht="58" customHeight="1">
       <x:c r="A6" s="16" t="str">
         <x:v>Newsletter</x:v>
       </x:c>
@@ -937,19 +1105,15 @@
         <x:v>Email, préférences</x:v>
       </x:c>
       <x:c r="E6" s="16" t="str">
-        <x:v>Consentement / règles de prospection</x:v>
+        <x:v>Marketing</x:v>
       </x:c>
       <x:c r="F6" s="16" t="str">
-        <x:v>3 ans après dernier contact</x:v>
-      </x:c>
-      <x:c r="G6" s="16" t="str">
-        <x:v>Marketing</x:v>
-      </x:c>
-      <x:c r="H6" s="16" t="str">
-        <x:v>Désinscription automatisée.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>Aucun accès à l'outil newsletter n'est signalé dans les pièces fournies.</x:v>
+      </x:c>
+      <x:c r="G6" s="16"/>
+      <x:c r="H6" s="16"/>
+    </x:row>
+    <x:row r="7" ht="58" customHeight="1">
       <x:c r="A7" s="16" t="str">
         <x:v>SAV / retours</x:v>
       </x:c>
@@ -963,19 +1127,15 @@
         <x:v>Identité, coordonnées, commande, motif</x:v>
       </x:c>
       <x:c r="E7" s="16" t="str">
-        <x:v>Contrat</x:v>
+        <x:v>Service clients, logistique</x:v>
       </x:c>
       <x:c r="F7" s="16" t="str">
-        <x:v>5 ans</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="str">
-        <x:v>Service clients, logistique</x:v>
-      </x:c>
-      <x:c r="H7" s="16" t="str">
-        <x:v>Exports CSV ponctuels non recensés.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>Des exports CSV ponctuels existent ; rapprochez cette information du fichier cité dans la chronologie.</x:v>
+      </x:c>
+      <x:c r="G7" s="16"/>
+      <x:c r="H7" s="16"/>
+    </x:row>
+    <x:row r="8" ht="58" customHeight="1">
       <x:c r="A8" s="16" t="str">
         <x:v>CRM revendeurs</x:v>
       </x:c>
@@ -989,19 +1149,15 @@
         <x:v>Nom, email pro, téléphone pro, historique</x:v>
       </x:c>
       <x:c r="E8" s="16" t="str">
-        <x:v>Intérêt légitime / contrat</x:v>
+        <x:v>Commercial</x:v>
       </x:c>
       <x:c r="F8" s="16" t="str">
-        <x:v>5 ans après fin de relation</x:v>
-      </x:c>
-      <x:c r="G8" s="16" t="str">
-        <x:v>Commercial</x:v>
-      </x:c>
-      <x:c r="H8" s="16" t="str">
-        <x:v>Droits d'accès à revoir après mobilité interne.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
+        <x:v>Une tentative d'accès est signalée ; un accès effectif n'est pas établi à ce stade.</x:v>
+      </x:c>
+      <x:c r="G8" s="16"/>
+      <x:c r="H8" s="16"/>
+    </x:row>
+    <x:row r="9" ht="58" customHeight="1">
       <x:c r="A9" s="16" t="str">
         <x:v>RH salariés</x:v>
       </x:c>
@@ -1015,25 +1171,276 @@
         <x:v>État civil, coordonnées, paie, absences</x:v>
       </x:c>
       <x:c r="E9" s="16" t="str">
-        <x:v>Obligation légale / contrat</x:v>
+        <x:v>RH, direction, prestataire paie</x:v>
       </x:c>
       <x:c r="F9" s="16" t="str">
-        <x:v>Selon obligations</x:v>
-      </x:c>
-      <x:c r="G9" s="16" t="str">
-        <x:v>RH, direction, prestataire paie</x:v>
-      </x:c>
-      <x:c r="H9" s="16" t="str">
-        <x:v>Droits d'accès trop larges sur dossier partagé.</x:v>
-      </x:c>
+        <x:v>Le dossier RH est distinct ; la présence de salariés testeurs dans un fichier client ne prouve pas un accès au dossier RH.</x:v>
+      </x:c>
+      <x:c r="G9" s="16"/>
+      <x:c r="H9" s="16"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A1:F1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R160853291eec4c64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba17837140e449b1"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="36" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="28" t="str">
+        <x:v>SCÉNARIO PÉDAGOGIQUE SIMULÉ — les informations de sauvegarde ci-dessous sont fictives et servent uniquement à l’analyse.</x:v>
+      </x:c>
+      <x:c r="B1" s="28"/>
+      <x:c r="C1" s="28"/>
+      <x:c r="D1" s="28"/>
+      <x:c r="E1" s="28"/>
+      <x:c r="F1" s="28"/>
+      <x:c r="G1" s="28"/>
+      <x:c r="H1" s="28"/>
+      <x:c r="I1" s="28"/>
+      <x:c r="K1"/>
+    </x:row>
+    <x:row r="2" ht="46" customHeight="1">
+      <x:c r="A2" s="52" t="str">
+        <x:v>Pour conclure, croisez les copies réellement identifiées, les supports/localisations, l’existence d’une copie hors ligne et les tests de restauration. Une fréquence annoncée ne prouve pas qu’une restauration fonctionnerait.</x:v>
+      </x:c>
+      <x:c r="B2" s="52"/>
+      <x:c r="C2" s="52"/>
+      <x:c r="D2" s="52"/>
+      <x:c r="E2" s="52"/>
+      <x:c r="F2" s="52"/>
+      <x:c r="G2" s="52"/>
+      <x:c r="H2" s="52"/>
+      <x:c r="I2" s="52"/>
+    </x:row>
+    <x:row r="3" ht="40" customHeight="1">
+      <x:c r="A3" s="30" t="str">
+        <x:v>Système / données</x:v>
+      </x:c>
+      <x:c r="B3" s="30" t="str">
+        <x:v>Donnée ou service d'origine</x:v>
+      </x:c>
+      <x:c r="C3" s="30" t="str">
+        <x:v>Copie / sauvegarde 1</x:v>
+      </x:c>
+      <x:c r="D3" s="30" t="str">
+        <x:v>Copie / sauvegarde 2</x:v>
+      </x:c>
+      <x:c r="E3" s="30" t="str">
+        <x:v>Localisation / support</x:v>
+      </x:c>
+      <x:c r="F3" s="30" t="str">
+        <x:v>Copie isolée ou déconnectée ?</x:v>
+      </x:c>
+      <x:c r="G3" s="30" t="str">
+        <x:v>Fréquence</x:v>
+      </x:c>
+      <x:c r="H3" s="30" t="str">
+        <x:v>Dernier test de restauration</x:v>
+      </x:c>
+      <x:c r="I3" s="30" t="str">
+        <x:v>Observation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="31" t="str">
+        <x:v>Site e-commerce</x:v>
+      </x:c>
+      <x:c r="B4" s="31" t="str">
+        <x:v>Base de données hébergée chez le prestataire</x:v>
+      </x:c>
+      <x:c r="C4" s="31" t="str">
+        <x:v>Instantané quotidien chez le même prestataire</x:v>
+      </x:c>
+      <x:c r="D4" s="31" t="str">
+        <x:v>Export hebdomadaire vers le NAS local</x:v>
+      </x:c>
+      <x:c r="E4" s="31" t="str">
+        <x:v>Cloud + NAS du site de Romans</x:v>
+      </x:c>
+      <x:c r="F4" s="31" t="str">
+        <x:v>Non démontré</x:v>
+      </x:c>
+      <x:c r="G4" s="31" t="str">
+        <x:v>Quotidienne + hebdomadaire</x:v>
+      </x:c>
+      <x:c r="H4" s="31" t="str">
+        <x:v>14/02/2026</x:v>
+      </x:c>
+      <x:c r="I4" s="31" t="str">
+        <x:v>La seconde copie reste accessible depuis le réseau interne.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="31" t="str">
+        <x:v>NAS local</x:v>
+      </x:c>
+      <x:c r="B5" s="31" t="str">
+        <x:v>Documents partagés de l'entreprise</x:v>
+      </x:c>
+      <x:c r="C5" s="31" t="str">
+        <x:v>Synchronisation quotidienne vers un second NAS</x:v>
+      </x:c>
+      <x:c r="D5" s="31" t="str">
+        <x:v>Aucune autre copie identifiée</x:v>
+      </x:c>
+      <x:c r="E5" s="31" t="str">
+        <x:v>Deux équipements sur le même réseau local</x:v>
+      </x:c>
+      <x:c r="F5" s="31" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G5" s="31" t="str">
+        <x:v>Quotidienne</x:v>
+      </x:c>
+      <x:c r="H5" s="31" t="str">
+        <x:v>27/01/2026</x:v>
+      </x:c>
+      <x:c r="I5" s="31" t="str">
+        <x:v>Les deux équipements restent connectés au même réseau.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="31" t="str">
+        <x:v>CRM revendeurs</x:v>
+      </x:c>
+      <x:c r="B6" s="31" t="str">
+        <x:v>Données hébergées dans le CRM</x:v>
+      </x:c>
+      <x:c r="C6" s="31" t="str">
+        <x:v>Sauvegarde du fournisseur</x:v>
+      </x:c>
+      <x:c r="D6" s="31" t="str">
+        <x:v>Export CSV mensuel sur le dossier partagé</x:v>
+      </x:c>
+      <x:c r="E6" s="31" t="str">
+        <x:v>Cloud fournisseur + NAS local</x:v>
+      </x:c>
+      <x:c r="F6" s="31" t="str">
+        <x:v>Non démontré</x:v>
+      </x:c>
+      <x:c r="G6" s="31" t="str">
+        <x:v>Hebdomadaire / mensuelle</x:v>
+      </x:c>
+      <x:c r="H6" s="31" t="str">
+        <x:v>03/11/2025</x:v>
+      </x:c>
+      <x:c r="I6" s="31" t="str">
+        <x:v>Le fonctionnement et l'isolement de la sauvegarde fournisseur ne sont pas documentés.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="31" t="str">
+        <x:v>Dossier RH</x:v>
+      </x:c>
+      <x:c r="B7" s="31" t="str">
+        <x:v>Dossier partagé RH</x:v>
+      </x:c>
+      <x:c r="C7" s="31" t="str">
+        <x:v>Sauvegarde quotidienne vers le NAS</x:v>
+      </x:c>
+      <x:c r="D7" s="31" t="str">
+        <x:v>Aucune autre copie identifiée</x:v>
+      </x:c>
+      <x:c r="E7" s="31" t="str">
+        <x:v>NAS local</x:v>
+      </x:c>
+      <x:c r="F7" s="31" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G7" s="31" t="str">
+        <x:v>Quotidienne</x:v>
+      </x:c>
+      <x:c r="H7" s="31" t="str">
+        <x:v>18/06/2026</x:v>
+      </x:c>
+      <x:c r="I7" s="31" t="str">
+        <x:v>Aucune copie hors réseau n'est identifiée dans les pièces disponibles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="31" t="str">
+        <x:v>Logiciel comptable</x:v>
+      </x:c>
+      <x:c r="B8" s="31" t="str">
+        <x:v>Application hébergée</x:v>
+      </x:c>
+      <x:c r="C8" s="31" t="str">
+        <x:v>Sauvegarde quotidienne du prestataire</x:v>
+      </x:c>
+      <x:c r="D8" s="31" t="str">
+        <x:v>Export mensuel chiffré sur disque externe</x:v>
+      </x:c>
+      <x:c r="E8" s="31" t="str">
+        <x:v>Cloud prestataire + disque conservé dans les bureaux</x:v>
+      </x:c>
+      <x:c r="F8" s="31" t="str">
+        <x:v>Partielle</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="str">
+        <x:v>Quotidienne + mensuelle</x:v>
+      </x:c>
+      <x:c r="H8" s="31" t="str">
+        <x:v>02/09/2026</x:v>
+      </x:c>
+      <x:c r="I8" s="31" t="str">
+        <x:v>Le disque n'est pas stocké hors site ; sa déconnexion entre deux exports est à confirmer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="31" t="str">
+        <x:v>Postes atelier</x:v>
+      </x:c>
+      <x:c r="B9" s="31" t="str">
+        <x:v>Fichiers locaux et données de production</x:v>
+      </x:c>
+      <x:c r="C9" s="31" t="str">
+        <x:v>Copie hebdomadaire vers le NAS</x:v>
+      </x:c>
+      <x:c r="D9" s="31" t="str">
+        <x:v>Aucune autre copie identifiée</x:v>
+      </x:c>
+      <x:c r="E9" s="31" t="str">
+        <x:v>NAS local</x:v>
+      </x:c>
+      <x:c r="F9" s="31" t="str">
+        <x:v>Non</x:v>
+      </x:c>
+      <x:c r="G9" s="31" t="str">
+        <x:v>Hebdomadaire</x:v>
+      </x:c>
+      <x:c r="H9" s="31" t="str">
+        <x:v>Jamais</x:v>
+      </x:c>
+      <x:c r="I9" s="31" t="str">
+        <x:v>Deux postes ne sont pas chiffrés ; aucun test de restauration n'est tracé.</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:I1"/>
+    <x:mergeCell ref="A2:I2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>